--- a/resources/templates/standard/A4200-02.xlsx
+++ b/resources/templates/standard/A4200-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>기록 분류표</t>
   </si>
@@ -580,12 +583,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.65" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -617,25 +622,25 @@
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT1" s="4"/>
       <c r="AU1" s="4"/>
@@ -789,7 +794,7 @@
     </row>
     <row r="5" ht="18.65" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -806,7 +811,7 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
       <c r="P5" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
@@ -823,7 +828,7 @@
       <c r="AC5" s="8"/>
       <c r="AD5" s="8"/>
       <c r="AE5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5" s="9"/>
       <c r="AG5" s="9"/>
@@ -836,7 +841,7 @@
       <c r="AN5" s="8"/>
       <c r="AO5" s="8"/>
       <c r="AP5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" s="9"/>
       <c r="AR5" s="9"/>
@@ -846,11 +851,11 @@
     </row>
     <row r="6" ht="18.65" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -861,7 +866,7 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -879,7 +884,7 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
@@ -887,13 +892,13 @@
       <c r="AF6" s="11"/>
       <c r="AG6" s="11"/>
       <c r="AH6" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI6" s="11"/>
       <c r="AJ6" s="11"/>
       <c r="AK6" s="11"/>
       <c r="AL6" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" s="11"/>
       <c r="AN6" s="11"/>
@@ -901,7 +906,7 @@
       <c r="AP6" s="11"/>
       <c r="AQ6" s="11"/>
       <c r="AR6" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS6" s="11"/>
       <c r="AT6" s="11"/>
@@ -911,17 +916,17 @@
       <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
@@ -942,15 +947,15 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC7" s="11"/>
       <c r="AD7" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE7" s="11"/>
       <c r="AF7" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" s="11"/>
       <c r="AH7" s="11"/>
@@ -958,15 +963,15 @@
       <c r="AJ7" s="11"/>
       <c r="AK7" s="11"/>
       <c r="AL7" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM7" s="11"/>
       <c r="AN7" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO7" s="11"/>
       <c r="AP7" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ7" s="11"/>
       <c r="AR7" s="11"/>
